--- a/packages/GB Accounts Company 2027-10-31 (Oct27) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Company 2027-10-31 (Oct27) Excel 2007/Financialaccounts.xlsx
@@ -55397,7 +55397,7 @@
         <v>150</v>
       </c>
       <c r="AA177" s="522" t="str">
-        <f>IF((CorporationTax!H15+CorporationTax!H17)&gt;0,CorporationTax!H15+CorporationTax!H17," ")</f>
+        <f>IF((CorporationTax!I15+CorporationTax!I17)&gt;0,CorporationTax!I15+CorporationTax!I17," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AB177" s="522"/>
@@ -55415,7 +55415,7 @@
         <v>150</v>
       </c>
       <c r="AL177" s="522" t="str">
-        <f>IF(CorporationTax!H18&lt;&gt;0,CorporationTax!H18," ")</f>
+        <f>IF(CorporationTax!I18&lt;&gt;0,CorporationTax!I18," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AM177" s="522"/>
@@ -55507,7 +55507,7 @@
         <v>150</v>
       </c>
       <c r="AA179" s="522" t="str">
-        <f>IF(CorporationTax!H16&gt;0,CorporationTax!H16," ")</f>
+        <f>IF(CorporationTax!I16&gt;0,CorporationTax!I16," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AB179" s="522"/>

--- a/packages/GB Accounts Company 2027-10-31 (Oct27) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Company 2027-10-31 (Oct27) Excel 2007/Financialaccounts.xlsx
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="626">
   <si>
     <t>Depreciation</t>
   </si>
@@ -2159,6 +2159,12 @@
   </si>
   <si>
     <t>(Small profits rate)</t>
+  </si>
+  <si>
+    <t>Copyright (C) 2006-2026 DIY Accounting Limited</t>
+  </si>
+  <si>
+    <t>Licensed under the PolyForm Internal Use License 1.0.0 with an additional grant for accountants. Free to use, source available: https://spreadsheets.diyaccounting.co.uk</t>
   </si>
 </sst>
 </file>
@@ -11957,7 +11963,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R86"/>
+  <dimension ref="A1:R89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="11" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="0.83203125" style="6" customWidth="1"/>
@@ -13448,6 +13454,16 @@
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
+    </row>
+    <row r="88">
+      <c r="B88" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="s">
+        <v>625</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="19">

--- a/packages/GB Accounts Company 2027-10-31 (Oct27) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Company 2027-10-31 (Oct27) Excel 2007/Financialaccounts.xlsx
@@ -12112,9 +12112,13 @@
       </c>
       <c r="M6" s="348"/>
       <c r="N6" s="170"/>
-      <c r="O6" s="151"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
+      <c r="O6" s="338" t="inlineStr">
+        <is>
+          <t>Franked investment income</t>
+        </is>
+      </c>
+      <c r="P6" s="339"/>
+      <c r="Q6" s="11"/>
       <c r="R6" s="3"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.15">
@@ -13466,7 +13470,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="G10:K10"/>
     <mergeCell ref="E5:H5"/>
@@ -13485,6 +13489,7 @@
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="O5:P5"/>
+    <mergeCell ref="O6:P6"/>
     <mergeCell ref="J6:K6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -16259,7 +16264,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1.5" style="256" customWidth="1"/>
@@ -16383,7 +16388,7 @@
       <c r="P4" s="253"/>
       <c r="Q4" s="253"/>
     </row>
-    <row r="5" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="253"/>
       <c r="B5" s="330">
         <f>DATE(YEAR(B6),MONTH(B6),1)</f>
@@ -16413,8 +16418,28 @@
         <v>623</v>
       </c>
       <c r="Q5" s="255"/>
-    </row>
-    <row r="6" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R5" s="253" t="inlineStr">
+        <is>
+          <t>(Main rate %)</t>
+        </is>
+      </c>
+      <c r="S5" s="253" t="inlineStr">
+        <is>
+          <t>(Relief fraction)</t>
+        </is>
+      </c>
+      <c r="T5" s="253" t="inlineStr">
+        <is>
+          <t>(Relief lower limit)</t>
+        </is>
+      </c>
+      <c r="U5" s="253" t="inlineStr">
+        <is>
+          <t>(Relief upper limit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="253"/>
       <c r="B6" s="330">
         <f>DATE(YEAR(B8),MONTH(B8),1)-1</f>
@@ -16457,8 +16482,20 @@
       <c r="Q6" s="255" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R6" s="310">
+        <v>25</v>
+      </c>
+      <c r="S6" s="262">
+        <v>0.015</v>
+      </c>
+      <c r="T6" s="262">
+        <v>50000</v>
+      </c>
+      <c r="U6" s="262">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="253"/>
       <c r="B7" s="330">
         <f>DATE(YEAR(B8),MONTH(B8),1)</f>
@@ -16500,6 +16537,18 @@
       </c>
       <c r="Q7" s="255" t="s">
         <v>268</v>
+      </c>
+      <c r="R7" s="310">
+        <v>25</v>
+      </c>
+      <c r="S7" s="262">
+        <v>0.015</v>
+      </c>
+      <c r="T7" s="262">
+        <v>50000</v>
+      </c>
+      <c r="U7" s="262">
+        <v>250000</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -16521,23 +16570,15 @@
         <v>14</v>
       </c>
       <c r="H8" s="253"/>
-      <c r="I8" s="185" t="inlineStr">
-        <is>
-          <t>Corporation Tax main rate</t>
-        </is>
-      </c>
+      <c r="I8" s="185"/>
       <c r="J8" s="253"/>
       <c r="K8" s="253"/>
       <c r="L8" s="253"/>
       <c r="M8" s="253"/>
       <c r="N8" s="253"/>
       <c r="O8" s="253"/>
-      <c r="P8" s="310">
-        <v>25</v>
-      </c>
-      <c r="Q8" s="255" t="s">
-        <v>268</v>
-      </c>
+      <c r="P8" s="310"/>
+      <c r="Q8" s="255"/>
     </row>
     <row r="9" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="253"/>
@@ -16551,11 +16592,7 @@
       <c r="F9" s="253"/>
       <c r="G9" s="255"/>
       <c r="H9" s="253"/>
-      <c r="I9" s="185" t="inlineStr">
-        <is>
-          <t>Marginal relief fraction</t>
-        </is>
-      </c>
+      <c r="I9" s="185"/>
       <c r="J9" s="253"/>
       <c r="K9" s="253"/>
       <c r="L9" s="262" t="s">
@@ -16566,9 +16603,7 @@
         <v>521</v>
       </c>
       <c r="O9" s="263"/>
-      <c r="P9" s="262">
-        <v>0.015</v>
-      </c>
+      <c r="P9" s="262"/>
       <c r="Q9" s="255"/>
     </row>
     <row r="10" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -16645,20 +16680,14 @@
       <c r="F12" s="253"/>
       <c r="G12" s="255"/>
       <c r="H12" s="253"/>
-      <c r="I12" s="185" t="inlineStr">
-        <is>
-          <t>Marginal relief lower limit</t>
-        </is>
-      </c>
+      <c r="I12" s="185"/>
       <c r="J12" s="253"/>
       <c r="K12" s="253"/>
       <c r="L12" s="253"/>
       <c r="M12" s="265"/>
       <c r="N12" s="255"/>
       <c r="O12" s="253"/>
-      <c r="P12" s="262">
-        <v>50000</v>
-      </c>
+      <c r="P12" s="262"/>
       <c r="Q12" s="255"/>
     </row>
     <row r="13" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -16677,20 +16706,14 @@
         <v>268</v>
       </c>
       <c r="H13" s="253"/>
-      <c r="I13" s="185" t="inlineStr">
-        <is>
-          <t>Marginal relief upper limit</t>
-        </is>
-      </c>
+      <c r="I13" s="185"/>
       <c r="J13" s="253"/>
       <c r="K13" s="253"/>
       <c r="L13" s="253"/>
       <c r="M13" s="253"/>
       <c r="N13" s="253"/>
       <c r="O13" s="253"/>
-      <c r="P13" s="262">
-        <v>250000</v>
-      </c>
+      <c r="P13" s="262"/>
       <c r="Q13" s="253"/>
     </row>
     <row r="14" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -44899,7 +44922,11 @@
     </row>
     <row r="29" spans="1:12" s="40" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A29" s="159"/>
-      <c r="B29" s="39"/>
+      <c r="B29" s="306" t="inlineStr">
+        <is>
+          <t>Add franked investment income (exempt distributions received)</t>
+        </is>
+      </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
       <c r="E29" s="157"/>
@@ -44908,12 +44935,19 @@
       <c r="H29" s="162"/>
       <c r="I29" s="161"/>
       <c r="J29" s="161"/>
-      <c r="K29" s="176"/>
+      <c r="K29" s="252">
+        <f>OpenAccounts!Q6</f>
+        <v>0</v>
+      </c>
       <c r="L29" s="39"/>
     </row>
     <row r="30" spans="1:12" s="40" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A30" s="158"/>
-      <c r="B30" s="39"/>
+      <c r="B30" s="306" t="inlineStr">
+        <is>
+          <t>Augmented profits, which the marginal relief limits are tested against</t>
+        </is>
+      </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
       <c r="E30" s="177"/>
@@ -44922,7 +44956,10 @@
       <c r="H30" s="162"/>
       <c r="I30" s="161"/>
       <c r="J30" s="161"/>
-      <c r="K30" s="161"/>
+      <c r="K30" s="252">
+        <f>K28+K29</f>
+        <v>0</v>
+      </c>
       <c r="L30" s="39"/>
     </row>
     <row r="31" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -44994,7 +45031,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="441">
-        <f>IF(F33&lt;=Admin!$P$12*A33/A35,Admin!P6,Admin!$P$8)</f>
+        <f>IF(K30*A33/A35&lt;=Admin!$T$6*A33/A35/(1+Admin!$P$14),Admin!P6,Admin!$R$6)</f>
         <v>19</v>
       </c>
       <c r="H33" s="442"/>
@@ -45008,7 +45045,7 @@
       </c>
       <c r="K33" s="161"/>
       <c r="L33" s="38">
-        <f>IF(AND(F33&gt;Admin!$P$12*A33/A35,F33&lt;Admin!$P$13*A33/A35),(Admin!$P$13*A33/A35-F33)*Admin!$P$9,0)</f>
+        <f>IF(AND(K30*A33/A35&gt;Admin!$T$6*A33/A35/(1+Admin!$P$14),K30*A33/A35&lt;Admin!$U$6*A33/A35/(1+Admin!$P$14)),(Admin!$U$6*A33/A35/(1+Admin!$P$14)-K30*A33/A35)*F33/(K30*A33/A35)*Admin!$S$6,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -45037,7 +45074,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="441">
-        <f>IF(F34&lt;=Admin!$P$12*A34/A35,Admin!P7,Admin!$P$8)</f>
+        <f>IF(K30*A34/A35&lt;=Admin!$T$7*A34/A35/(1+Admin!$P$14),Admin!P7,Admin!$R$7)</f>
         <v>19</v>
       </c>
       <c r="H34" s="442"/>
@@ -45051,7 +45088,7 @@
       </c>
       <c r="K34" s="161"/>
       <c r="L34" s="38">
-        <f>IF(AND(F34&gt;Admin!$P$12*A34/A35,F34&lt;Admin!$P$13*A34/A35),(Admin!$P$13*A34/A35-F34)*Admin!$P$9,0)</f>
+        <f>IF(AND(K30*A34/A35&gt;Admin!$T$7*A34/A35/(1+Admin!$P$14),K30*A34/A35&lt;Admin!$U$7*A34/A35/(1+Admin!$P$14)),(Admin!$U$7*A34/A35/(1+Admin!$P$14)-K30*A34/A35)*F34/(K30*A34/A35)*Admin!$S$7,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -52198,7 +52235,10 @@
       <c r="Y114" s="210" t="s">
         <v>150</v>
       </c>
-      <c r="Z114" s="514"/>
+      <c r="Z114" s="514">
+        <f>CorporationTax!K29</f>
+        <v>0</v>
+      </c>
       <c r="AA114" s="514"/>
       <c r="AB114" s="514"/>
       <c r="AC114" s="514"/>
@@ -52397,7 +52437,10 @@
         <v>40</v>
       </c>
       <c r="X118" s="553"/>
-      <c r="Y118" s="560"/>
+      <c r="Y118" s="560">
+        <f>Admin!$P$14</f>
+        <v>0</v>
+      </c>
       <c r="Z118" s="561"/>
       <c r="AA118" s="562"/>
       <c r="AB118" s="198"/>
@@ -52495,7 +52538,10 @@
         <v>41</v>
       </c>
       <c r="X120" s="553"/>
-      <c r="Y120" s="560"/>
+      <c r="Y120" s="560" t="str">
+        <f>IF(CorporationTax!A34&gt;0,Admin!$P$14," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
       <c r="Z120" s="561"/>
       <c r="AA120" s="562"/>
       <c r="AB120" s="198"/>
